--- a/quizzes/sculpture-16e-niveau2.xlsx
+++ b/quizzes/sculpture-16e-niveau2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF7D83F-E604-4A01-B054-A4906B03EB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E2A570D-8663-4807-951A-E6152790F2C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="288">
   <si>
     <t>image</t>
   </si>
@@ -424,9 +424,6 @@
     <t>Tombeau de Philippe le Beau et Jeanne la Folle</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/df/Base_pilone_Piazza_San_Marco_Venezia_Alessandro_de_Leopardi_3.jpg/1280px-Base_pilone_Piazza_San_Marco_Venezia_Alessandro_de_Leopardi_3.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Alessandro LEOPARDI</t>
   </si>
   <si>
@@ -469,21 +466,9 @@
     <t>Maître-autel</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4c/Palazzo_vecchio%2C_vincenzo_de%27_rossi%2C_fatiche_di_ercole_06.JPG/1280px-Palazzo_vecchio%2C_vincenzo_de%27_rossi%2C_fatiche_di_ercole_06.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Vincenzo DE' ROSSI</t>
-  </si>
-  <si>
-    <t>1562-1584</t>
-  </si>
-  <si>
     <t>Palazzo Vecchio, Florence</t>
   </si>
   <si>
-    <t>Les Travaux d'Hercule (série)</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/48/Giovanni_bandini%2C_giunone%2C_1570-73_ca.%2C_01.jpg/1280px-Giovanni_bandini%2C_giunone%2C_1570-73_ca.%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -604,9 +589,6 @@
     <t>Benedikt DREYER</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c7/00_2517_St.-Petri-Dom_zu_Schleswig_-_Bordesholmer_Altar.jpg/1280px-00_2517_St.-Petri-Dom_zu_Schleswig_-_Bordesholmer_Altar.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Hans BRÜGGEMANN</t>
   </si>
   <si>
@@ -634,9 +616,6 @@
     <t>Le Retable du maître-autel de Moosburg</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c2/Bigarny-Coro_Toledo_8%29.jpg/1280px-Bigarny-Coro_Toledo_8%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Felipe BIGARNY</t>
   </si>
   <si>
@@ -853,9 +832,6 @@
     <t>La Fontaine d'Auguste (Augustusbrunnen)</t>
   </si>
   <si>
-    <t>El Entierro de Cristo (Santo Entierro)</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f3/Capitole_de_Toulouse_-_Cour_Henri_IV_-_portail_de_Nicolas_Bachelier.jpg/1280px-Capitole_de_Toulouse_-_Cour_Henri_IV_-_portail_de_Nicolas_Bachelier.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -881,6 +857,33 @@
   </si>
   <si>
     <t>Autel du Saint-Sang (Heilig-Blut-Altar)</t>
+  </si>
+  <si>
+    <t>L'Enterrement du Christ</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9c/Grotta_del_buontalenti%2C_Paride_che_rapisce_Elena_di_Vincenzo_de%27_Rossi_03.JPG/960px-Grotta_del_buontalenti%2C_Paride_che_rapisce_Elena_di_Vincenzo_de%27_Rossi_03.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>L'Enlèvement d'Hélène par Pâris.</t>
+  </si>
+  <si>
+    <t>Jardin de Boboli, grotte de Buontalenti, Florence</t>
+  </si>
+  <si>
+    <t>Vincenzo de' ROSSI</t>
+  </si>
+  <si>
+    <t>vers 1560</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7d/Choir_stall_of_Cathedral_of_Toledo_06.jpg/960px-Choir_stall_of_Cathedral_of_Toledo_06.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/37/00_2516_Schleswig_%28Schleswig-Holstein%2C_Germany%29_-_Sankt-Petri-Dom.jpg/960px-00_2516_Schleswig_%28Schleswig-Holstein%2C_Germany%29_-_Sankt-Petri-Dom.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8d/Base_pilone_Piazza_San_Marco_Venezia_Alessandro_de_Leopardi_2_Mori.jpg/960px-Base_pilone_Piazza_San_Marco_Venezia_Alessandro_de_Leopardi_2_Mori.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -1021,7 +1024,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -1356,7 +1359,7 @@
     </row>
     <row r="2" spans="1:5" ht="14.25" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>5</v>
@@ -1372,25 +1375,25 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>137</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="14.25" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>9</v>
@@ -1399,15 +1402,15 @@
         <v>10</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="5" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>11</v>
@@ -1419,12 +1422,12 @@
         <v>13</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="5" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>14</v>
@@ -1433,7 +1436,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>16</v>
@@ -1441,7 +1444,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>17</v>
@@ -1458,7 +1461,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="15" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>21</v>
@@ -1492,7 +1495,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>24</v>
@@ -1509,19 +1512,19 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="8" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C11" s="9">
         <v>1525</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1543,7 +1546,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="8" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>126</v>
@@ -1560,24 +1563,24 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="12" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="5" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>33</v>
@@ -1594,19 +1597,19 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="D16" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="E16" s="7" t="s">
         <v>142</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1628,75 +1631,75 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>204</v>
+      <c r="A19" s="8" t="s">
+        <v>285</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="8" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C20" s="9">
         <v>1526</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>37</v>
@@ -1713,7 +1716,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>41</v>
@@ -1730,70 +1733,70 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D24" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="E24" s="7" t="s">
         <v>152</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="8" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C25" s="9">
         <v>1552</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="C26" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="D26" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="E26" s="7" t="s">
         <v>147</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1814,59 +1817,59 @@
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>194</v>
+      <c r="A29" s="8" t="s">
+        <v>286</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>49</v>
@@ -1878,7 +1881,7 @@
         <v>51</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1900,36 +1903,36 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="13" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="14" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1951,36 +1954,36 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="14" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="13" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1997,7 +2000,7 @@
         <v>13</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2036,27 +2039,27 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="8" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C42" s="9">
         <v>1545</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="8" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C43" s="9">
         <v>1500</v>
@@ -2065,7 +2068,7 @@
         <v>7</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2087,19 +2090,19 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="8" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2121,7 +2124,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>85</v>
@@ -2138,24 +2141,24 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="8" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C48" s="9">
         <v>1525</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="12" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>89</v>
@@ -2167,12 +2170,12 @@
         <v>91</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="8" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>92</v>
@@ -2181,15 +2184,15 @@
         <v>93</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>94</v>
@@ -2206,7 +2209,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="8" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>122</v>
@@ -2235,7 +2238,7 @@
         <v>100</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2257,24 +2260,24 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>101</v>
@@ -2286,7 +2289,7 @@
         <v>103</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2324,54 +2327,54 @@
       </c>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>149</v>
+      <c r="A59" s="8" t="s">
+        <v>280</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>150</v>
+        <v>283</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>151</v>
+        <v>284</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>152</v>
+        <v>282</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>153</v>
+        <v>281</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>93</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -2383,62 +2386,62 @@
     <hyperlink ref="A17" r:id="rId2" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
     <hyperlink ref="A54" r:id="rId3" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
     <hyperlink ref="A9" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="A3" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="A16" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="A26" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="A59" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="A24" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="A55" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="A34" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="A27" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="A60" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="A30" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="A29" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="A31" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="A19" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="A21" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="A18" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="A38" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="A61" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="A52" r:id="rId22" xr:uid="{051FAB9D-E09B-4ED9-81B3-096A5114ACBE}"/>
-    <hyperlink ref="A13" r:id="rId23" xr:uid="{4A92C66A-333A-40DF-BF53-EAF446598DCD}"/>
-    <hyperlink ref="A20" r:id="rId24" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/43/Sant%27Anna%2C_la_Madonna_e_il_Bambino_di_Francesco_da_Sangallo_%281526_circa%29%2C2.JPG/1280px-Sant%27Anna%2C_la_Madonna_e_il_Bambino_di_Francesco_da_Sangallo_%281526_circa%29%2C2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{2FF4392A-F97A-4E80-9BBD-DEC4E93BDC7C}"/>
-    <hyperlink ref="A45" r:id="rId25" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/ad/Fountain_of_Giant_-_Fontana_del_Gigante%2C_Naples_%285338%29.jpg/1280px-Fountain_of_Giant_-_Fontana_del_Gigante%2C_Naples_%285338%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{86E5581E-775C-45E9-A807-A9D9AB4CFDCB}"/>
-    <hyperlink ref="A37" r:id="rId26" xr:uid="{60C74D36-1782-4FEA-A5A2-AD5C80FF740D}"/>
-    <hyperlink ref="A42" r:id="rId27" xr:uid="{75F0EE8B-0188-4CBC-8FBD-4E0D4CD26F4E}"/>
-    <hyperlink ref="A48" r:id="rId28" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/42/Heiliger_Sebastian_%28Di%C3%B6zesanmuseum_Rottenburg%29-WUS07739.jpg/960px-Heiliger_Sebastian_%28Di%C3%B6zesanmuseum_Rottenburg%29-WUS07739.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9192D67D-C3D9-4D21-B8E1-AFE065B4D835}"/>
-    <hyperlink ref="A11" r:id="rId29" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/3b/Meeting_of_Saints_Joachim_and_Anne_at_the_Golden_Gate_MET_DP144435.jpg/960px-Meeting_of_Saints_Joachim_and_Anne_at_the_Golden_Gate_MET_DP144435.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C9D1EECD-7B81-4B3E-AC0B-5BB6E99845F0}"/>
-    <hyperlink ref="A25" r:id="rId30" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/44/Giovanni_battista_della_porta%2C_monumento_funebre_di_vespasiano_gonzaga%2C_1592%2C_con_statua_del_duca_di_leone_leoni%2C_1588%2C_01.jpg/960px-Giovanni_battista_della_porta%2C_monumento_funebre_di_vespasiano_gonzaga%2C_1592%2C_con_statua_del_duca_di_leone_leoni%2C_1588%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{BF171364-8EB8-4F3D-BDDE-2D2B5AF813A0}"/>
-    <hyperlink ref="A35" r:id="rId31" display="https://upload.wikimedia.org/wikipedia/commons/thumb/c/c9/Basilique_Saint-Denis_Louis_XII_Anne_de_Bretagne_tombeau.jpg/1280px-Basilique_Saint-Denis_Louis_XII_Anne_de_Bretagne_tombeau.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4F07312D-BEE3-4516-9B97-315121BE117D}"/>
-    <hyperlink ref="A2" r:id="rId32" xr:uid="{2077E551-C3F1-4C03-9D5A-001E1877B9CF}"/>
-    <hyperlink ref="A5" r:id="rId33" xr:uid="{204D6AED-007F-4278-B30C-A10FE8133F74}"/>
-    <hyperlink ref="A7" r:id="rId34" xr:uid="{74AE4E40-496F-40EE-B567-664D6CA3EFE6}"/>
-    <hyperlink ref="A10" r:id="rId35" xr:uid="{F2641063-B723-4687-A1B4-9A573CFA601D}"/>
-    <hyperlink ref="A12" r:id="rId36" xr:uid="{FB36D15C-7B4C-422D-8C8A-00E355D94FAD}"/>
-    <hyperlink ref="A22" r:id="rId37" xr:uid="{F28C5CC6-E841-4E14-A359-218192F01A0E}"/>
-    <hyperlink ref="A23" r:id="rId38" xr:uid="{3CF953F6-B51A-4334-A168-9B4F65A08B5F}"/>
-    <hyperlink ref="A28" r:id="rId39" xr:uid="{45E25862-21F5-44BD-BE8B-6E244590331D}"/>
-    <hyperlink ref="A33" r:id="rId40" xr:uid="{93339682-2137-4C1C-BF81-B53A6F82AAB3}"/>
-    <hyperlink ref="A36" r:id="rId41" xr:uid="{F36F5924-2B07-42A1-8C32-65A069DB6684}"/>
-    <hyperlink ref="A39" r:id="rId42" xr:uid="{190288CF-4C92-4B52-82B1-11BF290C5C9B}"/>
-    <hyperlink ref="A40" r:id="rId43" xr:uid="{E7063A7A-3A02-46F1-BF51-BCFC5907C76F}"/>
-    <hyperlink ref="A41" r:id="rId44" xr:uid="{EA121D01-B6C2-47EE-A6D3-F1A81DA2527A}"/>
-    <hyperlink ref="A44" r:id="rId45" xr:uid="{846D505A-C339-4E5E-9FDD-13DC33A3D1E2}"/>
-    <hyperlink ref="A51" r:id="rId46" xr:uid="{6A28EFF4-67DD-4336-A289-72CA75CAB64C}"/>
-    <hyperlink ref="A53" r:id="rId47" xr:uid="{6F6BD024-F89D-4BB9-98BA-58048B01814F}"/>
-    <hyperlink ref="A46" r:id="rId48" xr:uid="{F944014B-A423-4341-9507-11960FBFCBFA}"/>
-    <hyperlink ref="A6" r:id="rId49" xr:uid="{1E800B27-EF1A-4D0E-8B16-D9CBED06D4E3}"/>
-    <hyperlink ref="A57" r:id="rId50" xr:uid="{E1D21DC1-9E20-4633-A692-4D05E429BDE9}"/>
-    <hyperlink ref="A15" r:id="rId51" xr:uid="{721671E1-12C3-403F-BD55-E989121EBC81}"/>
-    <hyperlink ref="A47" r:id="rId52" xr:uid="{31EC43D0-F34C-4B1A-B478-E76E1EB0E63F}"/>
-    <hyperlink ref="A56" r:id="rId53" xr:uid="{8EFE1459-861E-4B8C-B847-110936D697EA}"/>
-    <hyperlink ref="A32" r:id="rId54" xr:uid="{EC689476-9E2C-45B3-A02B-6C72A267C600}"/>
-    <hyperlink ref="A50" r:id="rId55" xr:uid="{A8E8A90F-5C21-4804-9086-E46E7D39682F}"/>
-    <hyperlink ref="A4" r:id="rId56" xr:uid="{7FC32690-4F8A-438D-86D7-6E50EC280BD8}"/>
-    <hyperlink ref="A49" r:id="rId57" xr:uid="{D946CAC8-E7F9-4AF0-882F-2435201D1EE8}"/>
-    <hyperlink ref="A8" r:id="rId58" xr:uid="{5F9D5AAD-FAEC-4ABC-A3FF-B24A852491A7}"/>
-    <hyperlink ref="A14" r:id="rId59" xr:uid="{61A84FAB-2D8B-4E6F-908F-C9998DF2133B}"/>
-    <hyperlink ref="A43" r:id="rId60" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/02/La_Vierge_et_l%27Enfant_-_Michel_Colombe_-_Mus%C3%A9e_du_Louvre_Sculptures_RFML.SC.2022.39.1.jpg/960px-La_Vierge_et_l%27Enfant_-_Michel_Colombe_-_Mus%C3%A9e_du_Louvre_Sculptures_RFML.SC.2022.39.1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C34946D0-7C35-4DB2-B4F5-85355A667E33}"/>
+    <hyperlink ref="A16" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="A26" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="A24" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="A55" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="A34" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="A27" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="A60" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="A30" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="A31" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="A21" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="A18" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="A38" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="A61" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="A52" r:id="rId18" xr:uid="{051FAB9D-E09B-4ED9-81B3-096A5114ACBE}"/>
+    <hyperlink ref="A13" r:id="rId19" xr:uid="{4A92C66A-333A-40DF-BF53-EAF446598DCD}"/>
+    <hyperlink ref="A20" r:id="rId20" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/43/Sant%27Anna%2C_la_Madonna_e_il_Bambino_di_Francesco_da_Sangallo_%281526_circa%29%2C2.JPG/1280px-Sant%27Anna%2C_la_Madonna_e_il_Bambino_di_Francesco_da_Sangallo_%281526_circa%29%2C2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{2FF4392A-F97A-4E80-9BBD-DEC4E93BDC7C}"/>
+    <hyperlink ref="A45" r:id="rId21" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/ad/Fountain_of_Giant_-_Fontana_del_Gigante%2C_Naples_%285338%29.jpg/1280px-Fountain_of_Giant_-_Fontana_del_Gigante%2C_Naples_%285338%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{86E5581E-775C-45E9-A807-A9D9AB4CFDCB}"/>
+    <hyperlink ref="A37" r:id="rId22" xr:uid="{60C74D36-1782-4FEA-A5A2-AD5C80FF740D}"/>
+    <hyperlink ref="A42" r:id="rId23" xr:uid="{75F0EE8B-0188-4CBC-8FBD-4E0D4CD26F4E}"/>
+    <hyperlink ref="A48" r:id="rId24" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/42/Heiliger_Sebastian_%28Di%C3%B6zesanmuseum_Rottenburg%29-WUS07739.jpg/960px-Heiliger_Sebastian_%28Di%C3%B6zesanmuseum_Rottenburg%29-WUS07739.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9192D67D-C3D9-4D21-B8E1-AFE065B4D835}"/>
+    <hyperlink ref="A11" r:id="rId25" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/3b/Meeting_of_Saints_Joachim_and_Anne_at_the_Golden_Gate_MET_DP144435.jpg/960px-Meeting_of_Saints_Joachim_and_Anne_at_the_Golden_Gate_MET_DP144435.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C9D1EECD-7B81-4B3E-AC0B-5BB6E99845F0}"/>
+    <hyperlink ref="A25" r:id="rId26" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/44/Giovanni_battista_della_porta%2C_monumento_funebre_di_vespasiano_gonzaga%2C_1592%2C_con_statua_del_duca_di_leone_leoni%2C_1588%2C_01.jpg/960px-Giovanni_battista_della_porta%2C_monumento_funebre_di_vespasiano_gonzaga%2C_1592%2C_con_statua_del_duca_di_leone_leoni%2C_1588%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{BF171364-8EB8-4F3D-BDDE-2D2B5AF813A0}"/>
+    <hyperlink ref="A35" r:id="rId27" display="https://upload.wikimedia.org/wikipedia/commons/thumb/c/c9/Basilique_Saint-Denis_Louis_XII_Anne_de_Bretagne_tombeau.jpg/1280px-Basilique_Saint-Denis_Louis_XII_Anne_de_Bretagne_tombeau.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4F07312D-BEE3-4516-9B97-315121BE117D}"/>
+    <hyperlink ref="A2" r:id="rId28" xr:uid="{2077E551-C3F1-4C03-9D5A-001E1877B9CF}"/>
+    <hyperlink ref="A5" r:id="rId29" xr:uid="{204D6AED-007F-4278-B30C-A10FE8133F74}"/>
+    <hyperlink ref="A7" r:id="rId30" xr:uid="{74AE4E40-496F-40EE-B567-664D6CA3EFE6}"/>
+    <hyperlink ref="A10" r:id="rId31" xr:uid="{F2641063-B723-4687-A1B4-9A573CFA601D}"/>
+    <hyperlink ref="A12" r:id="rId32" xr:uid="{FB36D15C-7B4C-422D-8C8A-00E355D94FAD}"/>
+    <hyperlink ref="A22" r:id="rId33" xr:uid="{F28C5CC6-E841-4E14-A359-218192F01A0E}"/>
+    <hyperlink ref="A23" r:id="rId34" xr:uid="{3CF953F6-B51A-4334-A168-9B4F65A08B5F}"/>
+    <hyperlink ref="A28" r:id="rId35" xr:uid="{45E25862-21F5-44BD-BE8B-6E244590331D}"/>
+    <hyperlink ref="A33" r:id="rId36" xr:uid="{93339682-2137-4C1C-BF81-B53A6F82AAB3}"/>
+    <hyperlink ref="A36" r:id="rId37" xr:uid="{F36F5924-2B07-42A1-8C32-65A069DB6684}"/>
+    <hyperlink ref="A39" r:id="rId38" xr:uid="{190288CF-4C92-4B52-82B1-11BF290C5C9B}"/>
+    <hyperlink ref="A40" r:id="rId39" xr:uid="{E7063A7A-3A02-46F1-BF51-BCFC5907C76F}"/>
+    <hyperlink ref="A41" r:id="rId40" xr:uid="{EA121D01-B6C2-47EE-A6D3-F1A81DA2527A}"/>
+    <hyperlink ref="A44" r:id="rId41" xr:uid="{846D505A-C339-4E5E-9FDD-13DC33A3D1E2}"/>
+    <hyperlink ref="A51" r:id="rId42" xr:uid="{6A28EFF4-67DD-4336-A289-72CA75CAB64C}"/>
+    <hyperlink ref="A53" r:id="rId43" xr:uid="{6F6BD024-F89D-4BB9-98BA-58048B01814F}"/>
+    <hyperlink ref="A46" r:id="rId44" xr:uid="{F944014B-A423-4341-9507-11960FBFCBFA}"/>
+    <hyperlink ref="A6" r:id="rId45" xr:uid="{1E800B27-EF1A-4D0E-8B16-D9CBED06D4E3}"/>
+    <hyperlink ref="A57" r:id="rId46" xr:uid="{E1D21DC1-9E20-4633-A692-4D05E429BDE9}"/>
+    <hyperlink ref="A15" r:id="rId47" xr:uid="{721671E1-12C3-403F-BD55-E989121EBC81}"/>
+    <hyperlink ref="A47" r:id="rId48" xr:uid="{31EC43D0-F34C-4B1A-B478-E76E1EB0E63F}"/>
+    <hyperlink ref="A56" r:id="rId49" xr:uid="{8EFE1459-861E-4B8C-B847-110936D697EA}"/>
+    <hyperlink ref="A32" r:id="rId50" xr:uid="{EC689476-9E2C-45B3-A02B-6C72A267C600}"/>
+    <hyperlink ref="A50" r:id="rId51" xr:uid="{A8E8A90F-5C21-4804-9086-E46E7D39682F}"/>
+    <hyperlink ref="A4" r:id="rId52" xr:uid="{7FC32690-4F8A-438D-86D7-6E50EC280BD8}"/>
+    <hyperlink ref="A49" r:id="rId53" xr:uid="{D946CAC8-E7F9-4AF0-882F-2435201D1EE8}"/>
+    <hyperlink ref="A8" r:id="rId54" xr:uid="{5F9D5AAD-FAEC-4ABC-A3FF-B24A852491A7}"/>
+    <hyperlink ref="A14" r:id="rId55" xr:uid="{61A84FAB-2D8B-4E6F-908F-C9998DF2133B}"/>
+    <hyperlink ref="A43" r:id="rId56" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/02/La_Vierge_et_l%27Enfant_-_Michel_Colombe_-_Mus%C3%A9e_du_Louvre_Sculptures_RFML.SC.2022.39.1.jpg/960px-La_Vierge_et_l%27Enfant_-_Michel_Colombe_-_Mus%C3%A9e_du_Louvre_Sculptures_RFML.SC.2022.39.1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C34946D0-7C35-4DB2-B4F5-85355A667E33}"/>
+    <hyperlink ref="A59" r:id="rId57" display="https://upload.wikimedia.org/wikipedia/commons/thumb/9/9c/Grotta_del_buontalenti%2C_Paride_che_rapisce_Elena_di_Vincenzo_de%27_Rossi_03.JPG/960px-Grotta_del_buontalenti%2C_Paride_che_rapisce_Elena_di_Vincenzo_de%27_Rossi_03.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B32D07DD-91F6-424E-874D-DF8B1B88E696}"/>
+    <hyperlink ref="A19" r:id="rId58" xr:uid="{482FCC06-FE30-4052-9657-1B84B8DEBE57}"/>
+    <hyperlink ref="A29" r:id="rId59" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/37/00_2516_Schleswig_%28Schleswig-Holstein%2C_Germany%29_-_Sankt-Petri-Dom.jpg/960px-00_2516_Schleswig_%28Schleswig-Holstein%2C_Germany%29_-_Sankt-Petri-Dom.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C69CE810-F86B-4CF7-B637-90FEF0529308}"/>
+    <hyperlink ref="A3" r:id="rId60" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8d/Base_pilone_Piazza_San_Marco_Venezia_Alessandro_de_Leopardi_2_Mori.jpg/960px-Base_pilone_Piazza_San_Marco_Venezia_Alessandro_de_Leopardi_2_Mori.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C6218DCF-3F5B-4A3F-AB95-BAB16FF5A2CA}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
